--- a/data/trans_orig/P1432-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1432-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2007</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11158</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24112</t>
+          <t>24456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>676489</t>
+          <t>677319</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>690153</t>
+          <t>690187</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>677193</t>
+          <t>676728</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>686410</t>
+          <t>686642</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1358251</t>
+          <t>1357907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1374357</t>
+          <t>1374257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17472</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17731</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39504</t>
+          <t>39763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>944328</t>
+          <t>943539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>956895</t>
+          <t>956766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>942182</t>
+          <t>941151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>958883</t>
+          <t>958647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1890689</t>
+          <t>1890430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1912462</t>
+          <t>1912363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>14279</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27338</t>
+          <t>28283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>664241</t>
+          <t>664230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>675902</t>
+          <t>675830</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>664963</t>
+          <t>664350</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>677889</t>
+          <t>677812</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1335012</t>
+          <t>1334067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1351598</t>
+          <t>1351452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29377</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18717</t>
+          <t>18389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39375</t>
+          <t>38739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>925390</t>
+          <t>925812</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1009235</t>
+          <t>1010609</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1027652</t>
+          <t>1027758</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1941459</t>
+          <t>1942095</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1962117</t>
+          <t>1962445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>49392</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37704</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65998</t>
+          <t>68044</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70998</t>
+          <t>68992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106205</t>
+          <t>106354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3227563</t>
+          <t>3227151</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3250501</t>
+          <t>3250063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3313199</t>
+          <t>3311153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3341493</t>
+          <t>3340889</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6549536</t>
+          <t>6549387</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6584743</t>
+          <t>6586749</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2012</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24933</t>
+          <t>25787</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27157</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>695369</t>
+          <t>696398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>672117</t>
+          <t>671263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>688770</t>
+          <t>688443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1373362</t>
+          <t>1371064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1390359</t>
+          <t>1390021</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>16135</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25472</t>
+          <t>24272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>34801</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1001780</t>
+          <t>1001812</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1015806</t>
+          <t>1015819</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1003501</t>
+          <t>1004701</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1020138</t>
+          <t>1020116</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2013179</t>
+          <t>2012120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2033821</t>
+          <t>2032851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28680</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>744333</t>
+          <t>744945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>755531</t>
+          <t>755534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>755042</t>
+          <t>754296</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770234</t>
+          <t>770060</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1505009</t>
+          <t>1504272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523131</t>
+          <t>1523382</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24173</t>
+          <t>24212</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14578</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34514</t>
+          <t>35470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>930609</t>
+          <t>931445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>944681</t>
+          <t>944722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1027728</t>
+          <t>1027689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1042912</t>
+          <t>1042941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1965126</t>
+          <t>1964170</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1985062</t>
+          <t>1984533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>34740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44781</t>
+          <t>43029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74842</t>
+          <t>75272</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62231</t>
+          <t>64090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100120</t>
+          <t>101372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3389650</t>
+          <t>3392039</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3412704</t>
+          <t>3413214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3479148</t>
+          <t>3478718</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3509209</t>
+          <t>3510961</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6880649</t>
+          <t>6879397</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6918538</t>
+          <t>6916679</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2016</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19899</t>
+          <t>19908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>25808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661964</t>
+          <t>662130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>672444</t>
+          <t>672405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652940</t>
+          <t>652931</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>666597</t>
+          <t>667125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1320870</t>
+          <t>1321831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1337480</t>
+          <t>1337518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>9625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>26607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1011635</t>
+          <t>1011545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1020525</t>
+          <t>1020602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1022630</t>
+          <t>1023017</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1037003</t>
+          <t>1037076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2038779</t>
+          <t>2038737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2055665</t>
+          <t>2055719</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9291</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22043</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28045</t>
+          <t>26796</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>750261</t>
+          <t>750358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>758662</t>
+          <t>758539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>762968</t>
+          <t>761982</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>778427</t>
+          <t>777947</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1516518</t>
+          <t>1517767</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1534603</t>
+          <t>1534925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26050</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>10781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29051</t>
+          <t>30253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>930347</t>
+          <t>931143</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>936785</t>
+          <t>936794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1017729</t>
+          <t>1017779</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1036057</t>
+          <t>1035509</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1952295</t>
+          <t>1951093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1971754</t>
+          <t>1970565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26742</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>38462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65875</t>
+          <t>69353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52845</t>
+          <t>53794</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88229</t>
+          <t>87626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3367608</t>
+          <t>3368071</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3383140</t>
+          <t>3383759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3478667</t>
+          <t>3475189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3506797</t>
+          <t>3506080</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6850663</t>
+          <t>6851266</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6886047</t>
+          <t>6885098</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1432-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1432-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24456</t>
+          <t>22684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>677319</t>
+          <t>677616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>690187</t>
+          <t>689927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>676728</t>
+          <t>676810</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>686642</t>
+          <t>686639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1357907</t>
+          <t>1359679</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1374257</t>
+          <t>1374553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>17554</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27242</t>
+          <t>28015</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>17546</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39763</t>
+          <t>39570</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>943539</t>
+          <t>944246</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>956766</t>
+          <t>956671</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>941151</t>
+          <t>940378</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>958647</t>
+          <t>958806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1890430</t>
+          <t>1890623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1912363</t>
+          <t>1912647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>14764</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>18863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28283</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>664230</t>
+          <t>663745</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>675830</t>
+          <t>675269</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>664350</t>
+          <t>664978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>677812</t>
+          <t>678014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1334067</t>
+          <t>1334185</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1351452</t>
+          <t>1351681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>18063</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10372</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27301</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>1,74%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18063</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10854</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>28003</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38739</t>
+          <t>39468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>925812</t>
+          <t>926384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>937191</t>
+          <t>937273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,47 +1889,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1020549</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1011311</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1028240</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>98,26%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>980</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1020549</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1010609</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1027758</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1942095</t>
+          <t>1941366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1962445</t>
+          <t>1962876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>26081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49392</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>37609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68044</t>
+          <t>66395</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68992</t>
+          <t>68472</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106354</t>
+          <t>106966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3227151</t>
+          <t>3226755</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3250063</t>
+          <t>3250462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3311153</t>
+          <t>3312802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3340889</t>
+          <t>3341588</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6549387</t>
+          <t>6548775</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6586749</t>
+          <t>6587269</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>9423</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25787</t>
+          <t>25683</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29455</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>696398</t>
+          <t>696383</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>671263</t>
+          <t>671367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>688443</t>
+          <t>687627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1371064</t>
+          <t>1370632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1390021</t>
+          <t>1389439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16135</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24272</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34801</t>
+          <t>35996</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1001812</t>
+          <t>1001047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1015819</t>
+          <t>1015812</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1004701</t>
+          <t>1004309</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1020116</t>
+          <t>1020197</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2012120</t>
+          <t>2010925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2032851</t>
+          <t>2033355</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12678</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21769</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29417</t>
+          <t>28616</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>744945</t>
+          <t>744234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>755534</t>
+          <t>754640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>754296</t>
+          <t>753761</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770060</t>
+          <t>769879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1504272</t>
+          <t>1505073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523382</t>
+          <t>1523674</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>17002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24212</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15107</t>
+          <t>14168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35470</t>
+          <t>33487</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>931445</t>
+          <t>930737</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>944722</t>
+          <t>944714</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1027689</t>
+          <t>1027704</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1042941</t>
+          <t>1042899</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1964170</t>
+          <t>1966153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1984533</t>
+          <t>1985472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13565</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34740</t>
+          <t>35835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43029</t>
+          <t>43559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75272</t>
+          <t>73835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64090</t>
+          <t>62191</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101372</t>
+          <t>100231</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3392039</t>
+          <t>3390944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3413214</t>
+          <t>3412516</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3478718</t>
+          <t>3480155</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3510961</t>
+          <t>3510431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6879397</t>
+          <t>6880538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6916679</t>
+          <t>6918578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>12864</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19908</t>
+          <t>20149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25808</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662130</t>
+          <t>661936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>672405</t>
+          <t>672490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652931</t>
+          <t>652690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>667125</t>
+          <t>667038</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1321831</t>
+          <t>1319636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1337518</t>
+          <t>1337259</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19896</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9625</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26607</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1011545</t>
+          <t>1010652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1020602</t>
+          <t>1020621</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1023017</t>
+          <t>1022448</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1037076</t>
+          <t>1036992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2038737</t>
+          <t>2038454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2055719</t>
+          <t>2055098</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>27134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>750358</t>
+          <t>750114</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>758539</t>
+          <t>758648</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>761982</t>
+          <t>762545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>777947</t>
+          <t>777906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1517767</t>
+          <t>1517429</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1534925</t>
+          <t>1534697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26874</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>27825</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>931143</t>
+          <t>930381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>936794</t>
+          <t>936783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1017779</t>
+          <t>1016905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1035509</t>
+          <t>1036042</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1951093</t>
+          <t>1953521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1970565</t>
+          <t>1971093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26279</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38462</t>
+          <t>35140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69353</t>
+          <t>67268</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53794</t>
+          <t>54011</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87626</t>
+          <t>88710</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3368071</t>
+          <t>3366565</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3383759</t>
+          <t>3383873</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3475189</t>
+          <t>3477274</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3506080</t>
+          <t>3509402</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6851266</t>
+          <t>6850182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6885098</t>
+          <t>6884881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
